--- a/MovieCatalog.xlsx
+++ b/MovieCatalog.xlsx
@@ -16,17 +16,17 @@
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1782869296" val="1224" rev="124" rev64="64" revOS="1" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1782869296" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1782869296" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1782869296"/>
+      <pm:revision xmlns:pm="smNativeData" day="1784680674" val="1224" rev="124" rev64="64" revOS="1" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1784680674" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1784680674" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1784680674"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2137" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2197" uniqueCount="445">
   <si>
     <t>Movie Name</t>
   </si>
@@ -1426,6 +1426,42 @@
   <si>
     <t>Zero Dark Thirty</t>
   </si>
+  <si>
+    <t>Blade Runner: Final Cut</t>
+  </si>
+  <si>
+    <t>Set-43</t>
+  </si>
+  <si>
+    <t>Shining (1980)</t>
+  </si>
+  <si>
+    <t>PCM 5.1</t>
+  </si>
+  <si>
+    <t>Lost Boys</t>
+  </si>
+  <si>
+    <t>Caddyshack</t>
+  </si>
+  <si>
+    <t>Lethal Weapon</t>
+  </si>
+  <si>
+    <t>A nightmare on Elm Street (1984)</t>
+  </si>
+  <si>
+    <t>Purple Rain</t>
+  </si>
+  <si>
+    <t>Full Metal Jacket</t>
+  </si>
+  <si>
+    <t>Tango &amp; Cash</t>
+  </si>
+  <si>
+    <t>Risky Business</t>
+  </si>
 </sst>
 </file>
 
@@ -1450,7 +1486,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1782869296" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784680674" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -1465,7 +1501,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1782869296" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784680674" ulstyle="none" kern="1">
             <pm:latin face="Basic Sans" sz="200" lang="default"/>
             <pm:cs face="Basic Roman" sz="200" lang="default"/>
             <pm:ea face="Basic Roman" sz="200" lang="default"/>
@@ -1481,7 +1517,7 @@
       <vertAlign val="superscript"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1782869296" ulstyle="none" kern="1" ssSize="66" ssDistance="15">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784680674" ulstyle="none" kern="1" ssSize="66" ssDistance="15">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -1497,7 +1533,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1782869296" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784680674" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -1519,7 +1555,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782869296" type="1" fgLvl="76" fgClr="00FFFF00" bgLvl="24" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1784680674" type="1" fgLvl="76" fgClr="00FFFF00" bgLvl="24" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1533,7 +1569,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782869296" type="1" fgLvl="76" fgClr="00FFFF00" bgLvl="24" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1784680674" type="1" fgLvl="76" fgClr="00FFFF00" bgLvl="24" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1547,7 +1583,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782869296" type="1" fgLvl="38" fgClr="00FFFF00" bgLvl="62" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1784680674" type="1" fgLvl="38" fgClr="00FFFF00" bgLvl="62" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1558,7 +1594,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782869296" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1784680674" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1580,7 +1616,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782869296"/>
+          <pm:border xmlns:pm="smNativeData" id="1784680674"/>
         </ext>
       </extLst>
     </border>
@@ -1599,7 +1635,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782869296">
+          <pm:border xmlns:pm="smNativeData" id="1784680674">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1623,7 +1659,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782869296">
+          <pm:border xmlns:pm="smNativeData" id="1784680674">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1647,7 +1683,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782869296">
+          <pm:border xmlns:pm="smNativeData" id="1784680674">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1670,7 +1706,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782869296">
+          <pm:border xmlns:pm="smNativeData" id="1784680674">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1693,7 +1729,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782869296"/>
+          <pm:border xmlns:pm="smNativeData" id="1784680674"/>
         </ext>
       </extLst>
     </border>
@@ -1712,7 +1748,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782869296"/>
+          <pm:border xmlns:pm="smNativeData" id="1784680674"/>
         </ext>
       </extLst>
     </border>
@@ -1735,10 +1771,10 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1782869296" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1784680674" count="1">
         <pm:charStyle name="Normal" fontId="0"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1782869296" count="2">
+      <pm:colors xmlns:pm="smNativeData" id="1784680674" count="2">
         <pm:color name="Color 24" rgb="FFFF3D"/>
         <pm:color name="Color 25" rgb="FFFF9E"/>
       </pm:colors>
@@ -2004,7 +2040,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:J353"/>
+  <dimension ref="A1:J363"/>
   <sheetFormatPr baseColWidth="9" defaultColWidth="10.000000" defaultRowHeight="13.45"/>
   <cols>
     <col min="1" max="1" width="43.783784" customWidth="1"/>
@@ -10525,6 +10561,206 @@
         <v>13</v>
       </c>
     </row>
+    <row r="354" spans="1:10">
+      <c r="A354" t="s">
+        <v>433</v>
+      </c>
+      <c r="C354" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F354" t="s">
+        <v>434</v>
+      </c>
+      <c r="H354" t="s">
+        <v>11</v>
+      </c>
+      <c r="I354" t="s">
+        <v>95</v>
+      </c>
+      <c r="J354" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="355" spans="1:10">
+      <c r="A355" t="s">
+        <v>435</v>
+      </c>
+      <c r="C355" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F355" t="s">
+        <v>434</v>
+      </c>
+      <c r="H355" t="s">
+        <v>436</v>
+      </c>
+      <c r="I355" t="s">
+        <v>95</v>
+      </c>
+      <c r="J355" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="356" spans="1:10">
+      <c r="A356" t="s">
+        <v>437</v>
+      </c>
+      <c r="C356" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F356" t="s">
+        <v>434</v>
+      </c>
+      <c r="H356" t="s">
+        <v>11</v>
+      </c>
+      <c r="I356" t="s">
+        <v>95</v>
+      </c>
+      <c r="J356" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="357" spans="1:10">
+      <c r="A357" t="s">
+        <v>438</v>
+      </c>
+      <c r="C357" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F357" t="s">
+        <v>434</v>
+      </c>
+      <c r="H357" t="s">
+        <v>18</v>
+      </c>
+      <c r="I357" t="s">
+        <v>95</v>
+      </c>
+      <c r="J357" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="358" spans="1:10">
+      <c r="A358" t="s">
+        <v>439</v>
+      </c>
+      <c r="C358" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F358" t="s">
+        <v>434</v>
+      </c>
+      <c r="H358" t="s">
+        <v>26</v>
+      </c>
+      <c r="I358" t="s">
+        <v>95</v>
+      </c>
+      <c r="J358" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="359" spans="1:10">
+      <c r="A359" t="s">
+        <v>440</v>
+      </c>
+      <c r="C359" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F359" t="s">
+        <v>434</v>
+      </c>
+      <c r="H359" t="s">
+        <v>23</v>
+      </c>
+      <c r="I359" t="s">
+        <v>95</v>
+      </c>
+      <c r="J359" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="360" spans="1:10">
+      <c r="A360" t="s">
+        <v>441</v>
+      </c>
+      <c r="C360" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F360" t="s">
+        <v>434</v>
+      </c>
+      <c r="H360" t="s">
+        <v>18</v>
+      </c>
+      <c r="I360" t="s">
+        <v>95</v>
+      </c>
+      <c r="J360" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="361" spans="1:10">
+      <c r="A361" t="s">
+        <v>442</v>
+      </c>
+      <c r="C361" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F361" t="s">
+        <v>434</v>
+      </c>
+      <c r="H361" t="s">
+        <v>436</v>
+      </c>
+      <c r="I361" t="s">
+        <v>95</v>
+      </c>
+      <c r="J361" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="362" spans="1:10">
+      <c r="A362" t="s">
+        <v>443</v>
+      </c>
+      <c r="C362" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F362" t="s">
+        <v>434</v>
+      </c>
+      <c r="H362" t="s">
+        <v>11</v>
+      </c>
+      <c r="I362" t="s">
+        <v>95</v>
+      </c>
+      <c r="J362" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="363" spans="1:10">
+      <c r="A363" t="s">
+        <v>444</v>
+      </c>
+      <c r="C363" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F363" t="s">
+        <v>434</v>
+      </c>
+      <c r="H363" t="s">
+        <v>11</v>
+      </c>
+      <c r="I363" t="s">
+        <v>95</v>
+      </c>
+      <c r="J363" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:XFD353">
     <sortState ref="A2:A353">
@@ -10534,7 +10770,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1782869296" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1784680674" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -10543,14 +10779,14 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1782869296" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1782869296" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:header xmlns:pm="smNativeData" id="1784680674" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1784680674" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1782869296" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1784680674" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/MovieCatalog.xlsx
+++ b/MovieCatalog.xlsx
@@ -16,10 +16,10 @@
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1784680674" val="1224" rev="124" rev64="64" revOS="1" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1784680674" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1784680674" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1784680674"/>
+      <pm:revision xmlns:pm="smNativeData" day="1785005472" val="1224" rev="124" rev64="64" revOS="1" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1785005472" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1785005472" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1785005472"/>
     </ext>
   </extLst>
 </workbook>
@@ -1486,7 +1486,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784680674" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785005472" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -1501,7 +1501,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784680674" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785005472" ulstyle="none" kern="1">
             <pm:latin face="Basic Sans" sz="200" lang="default"/>
             <pm:cs face="Basic Roman" sz="200" lang="default"/>
             <pm:ea face="Basic Roman" sz="200" lang="default"/>
@@ -1517,7 +1517,7 @@
       <vertAlign val="superscript"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784680674" ulstyle="none" kern="1" ssSize="66" ssDistance="15">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785005472" ulstyle="none" kern="1" ssSize="66" ssDistance="15">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -1533,7 +1533,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784680674" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785005472" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -1555,7 +1555,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784680674" type="1" fgLvl="76" fgClr="00FFFF00" bgLvl="24" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785005472" type="1" fgLvl="76" fgClr="00FFFF00" bgLvl="24" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1569,7 +1569,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784680674" type="1" fgLvl="76" fgClr="00FFFF00" bgLvl="24" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785005472" type="1" fgLvl="76" fgClr="00FFFF00" bgLvl="24" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1583,7 +1583,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784680674" type="1" fgLvl="38" fgClr="00FFFF00" bgLvl="62" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785005472" type="1" fgLvl="38" fgClr="00FFFF00" bgLvl="62" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1594,7 +1594,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784680674" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785005472" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1616,7 +1616,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784680674"/>
+          <pm:border xmlns:pm="smNativeData" id="1785005472"/>
         </ext>
       </extLst>
     </border>
@@ -1635,7 +1635,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784680674">
+          <pm:border xmlns:pm="smNativeData" id="1785005472">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1659,7 +1659,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784680674">
+          <pm:border xmlns:pm="smNativeData" id="1785005472">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1683,7 +1683,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784680674">
+          <pm:border xmlns:pm="smNativeData" id="1785005472">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1706,7 +1706,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784680674">
+          <pm:border xmlns:pm="smNativeData" id="1785005472">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1729,7 +1729,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784680674"/>
+          <pm:border xmlns:pm="smNativeData" id="1785005472"/>
         </ext>
       </extLst>
     </border>
@@ -1748,7 +1748,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784680674"/>
+          <pm:border xmlns:pm="smNativeData" id="1785005472"/>
         </ext>
       </extLst>
     </border>
@@ -1771,10 +1771,10 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1784680674" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1785005472" count="1">
         <pm:charStyle name="Normal" fontId="0"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1784680674" count="2">
+      <pm:colors xmlns:pm="smNativeData" id="1785005472" count="2">
         <pm:color name="Color 24" rgb="FFFF3D"/>
         <pm:color name="Color 25" rgb="FFFF9E"/>
       </pm:colors>
@@ -2043,7 +2043,7 @@
   <dimension ref="A1:J363"/>
   <sheetFormatPr baseColWidth="9" defaultColWidth="10.000000" defaultRowHeight="13.45"/>
   <cols>
-    <col min="1" max="1" width="43.783784" customWidth="1"/>
+    <col min="1" max="1" width="43.045045" customWidth="1"/>
     <col min="8" max="8" width="16.081081" customWidth="1"/>
     <col min="9" max="9" width="20.135135" customWidth="1"/>
     <col min="10" max="10" width="17.990991" customWidth="1"/>
@@ -9118,7 +9118,7 @@
         <v>1</v>
       </c>
       <c r="J293" t="s">
-        <v>13</v>
+        <v>122</v>
       </c>
     </row>
     <row r="294" spans="1:10">
@@ -9352,7 +9352,7 @@
         <v>1</v>
       </c>
       <c r="J303" t="s">
-        <v>13</v>
+        <v>122</v>
       </c>
     </row>
     <row r="304" spans="1:10">
@@ -10288,7 +10288,7 @@
         <v>1</v>
       </c>
       <c r="J342" t="s">
-        <v>13</v>
+        <v>122</v>
       </c>
     </row>
     <row r="343" spans="1:10">
@@ -10770,7 +10770,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1784680674" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1785005472" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -10779,14 +10779,14 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1784680674" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1784680674" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:header xmlns:pm="smNativeData" id="1785005472" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1785005472" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1784680674" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1785005472" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/MovieCatalog.xlsx
+++ b/MovieCatalog.xlsx
@@ -16,17 +16,17 @@
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1785005472" val="1224" rev="124" rev64="64" revOS="1" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1785005472" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1785005472" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1785005472"/>
+      <pm:revision xmlns:pm="smNativeData" day="1791932052" val="1224" rev="124" rev64="64" revOS="1" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1791932052" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1791932052" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1791932052"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2197" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2258" uniqueCount="455">
   <si>
     <t>Movie Name</t>
   </si>
@@ -1462,6 +1462,36 @@
   <si>
     <t>Risky Business</t>
   </si>
+  <si>
+    <t>Wild Robot</t>
+  </si>
+  <si>
+    <t>Ben-Hur</t>
+  </si>
+  <si>
+    <t>Bugonia</t>
+  </si>
+  <si>
+    <t>13 Hours</t>
+  </si>
+  <si>
+    <t>Jurassic World - Rebirth</t>
+  </si>
+  <si>
+    <t>Set-44</t>
+  </si>
+  <si>
+    <t>El Mariachi</t>
+  </si>
+  <si>
+    <t>DTS-HD MA 2.0</t>
+  </si>
+  <si>
+    <t>A Working Man</t>
+  </si>
+  <si>
+    <t>Ambulance</t>
+  </si>
 </sst>
 </file>
 
@@ -1486,7 +1516,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1785005472" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1791932052" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -1501,7 +1531,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1785005472" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1791932052" ulstyle="none" kern="1">
             <pm:latin face="Basic Sans" sz="200" lang="default"/>
             <pm:cs face="Basic Roman" sz="200" lang="default"/>
             <pm:ea face="Basic Roman" sz="200" lang="default"/>
@@ -1517,7 +1547,7 @@
       <vertAlign val="superscript"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1785005472" ulstyle="none" kern="1" ssSize="66" ssDistance="15">
+          <pm:charSpec xmlns:pm="smNativeData" id="1791932052" ulstyle="none" kern="1" ssSize="66" ssDistance="15">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -1533,7 +1563,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1785005472" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1791932052" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -1555,7 +1585,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1785005472" type="1" fgLvl="76" fgClr="00FFFF00" bgLvl="24" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1791932052" type="1" fgLvl="76" fgClr="00FFFF00" bgLvl="24" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1569,7 +1599,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1785005472" type="1" fgLvl="76" fgClr="00FFFF00" bgLvl="24" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1791932052" type="1" fgLvl="76" fgClr="00FFFF00" bgLvl="24" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1583,7 +1613,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1785005472" type="1" fgLvl="38" fgClr="00FFFF00" bgLvl="62" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1791932052" type="1" fgLvl="38" fgClr="00FFFF00" bgLvl="62" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1594,7 +1624,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1785005472" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1791932052" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1616,7 +1646,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1785005472"/>
+          <pm:border xmlns:pm="smNativeData" id="1791932052"/>
         </ext>
       </extLst>
     </border>
@@ -1635,7 +1665,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1785005472">
+          <pm:border xmlns:pm="smNativeData" id="1791932052">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1659,7 +1689,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1785005472">
+          <pm:border xmlns:pm="smNativeData" id="1791932052">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1683,7 +1713,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1785005472">
+          <pm:border xmlns:pm="smNativeData" id="1791932052">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1706,7 +1736,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1785005472">
+          <pm:border xmlns:pm="smNativeData" id="1791932052">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1729,7 +1759,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1785005472"/>
+          <pm:border xmlns:pm="smNativeData" id="1791932052"/>
         </ext>
       </extLst>
     </border>
@@ -1748,7 +1778,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1785005472"/>
+          <pm:border xmlns:pm="smNativeData" id="1791932052"/>
         </ext>
       </extLst>
     </border>
@@ -1771,10 +1801,10 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1785005472" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1791932052" count="1">
         <pm:charStyle name="Normal" fontId="0"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1785005472" count="2">
+      <pm:colors xmlns:pm="smNativeData" id="1791932052" count="2">
         <pm:color name="Color 24" rgb="FFFF3D"/>
         <pm:color name="Color 25" rgb="FFFF9E"/>
       </pm:colors>
@@ -2040,7 +2070,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:J363"/>
+  <dimension ref="A1:J373"/>
   <sheetFormatPr baseColWidth="9" defaultColWidth="10.000000" defaultRowHeight="13.45"/>
   <cols>
     <col min="1" max="1" width="43.045045" customWidth="1"/>
@@ -10761,6 +10791,209 @@
         <v>13</v>
       </c>
     </row>
+    <row r="364" spans="1:10">
+      <c r="A364" t="s">
+        <v>445</v>
+      </c>
+      <c r="C364" t="s">
+        <v>2</v>
+      </c>
+      <c r="E364" t="s">
+        <v>4</v>
+      </c>
+      <c r="G364" t="s">
+        <v>6</v>
+      </c>
+      <c r="H364" t="s">
+        <v>15</v>
+      </c>
+      <c r="I364" t="s">
+        <v>424</v>
+      </c>
+      <c r="J364" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="365" spans="1:10">
+      <c r="A365" t="s">
+        <v>446</v>
+      </c>
+      <c r="E365" t="s">
+        <v>4</v>
+      </c>
+      <c r="H365" t="s">
+        <v>15</v>
+      </c>
+      <c r="I365" t="s">
+        <v>47</v>
+      </c>
+      <c r="J365" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="366" spans="1:10">
+      <c r="A366" t="s">
+        <v>447</v>
+      </c>
+      <c r="C366" t="s">
+        <v>2</v>
+      </c>
+      <c r="E366" t="s">
+        <v>4</v>
+      </c>
+      <c r="G366" t="s">
+        <v>6</v>
+      </c>
+      <c r="H366" t="s">
+        <v>15</v>
+      </c>
+      <c r="I366" t="s">
+        <v>47</v>
+      </c>
+      <c r="J366" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="367" spans="1:10">
+      <c r="A367" t="s">
+        <v>448</v>
+      </c>
+      <c r="E367" t="s">
+        <v>4</v>
+      </c>
+      <c r="H367" t="s">
+        <v>15</v>
+      </c>
+      <c r="I367" t="s">
+        <v>12</v>
+      </c>
+      <c r="J367" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="368" spans="1:10">
+      <c r="A368" t="s">
+        <v>449</v>
+      </c>
+      <c r="C368" t="s">
+        <v>2</v>
+      </c>
+      <c r="E368" t="s">
+        <v>4</v>
+      </c>
+      <c r="G368" t="s">
+        <v>6</v>
+      </c>
+      <c r="H368" t="s">
+        <v>15</v>
+      </c>
+      <c r="I368" t="s">
+        <v>229</v>
+      </c>
+      <c r="J368" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="369" spans="1:10">
+      <c r="A369" t="s">
+        <v>113</v>
+      </c>
+      <c r="C369" t="s">
+        <v>2</v>
+      </c>
+      <c r="F369" t="s">
+        <v>450</v>
+      </c>
+      <c r="H369" t="s">
+        <v>18</v>
+      </c>
+      <c r="I369" t="s">
+        <v>126</v>
+      </c>
+      <c r="J369" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="370" spans="1:10">
+      <c r="A370" t="s">
+        <v>314</v>
+      </c>
+      <c r="C370" t="s">
+        <v>2</v>
+      </c>
+      <c r="F370" t="s">
+        <v>450</v>
+      </c>
+      <c r="H370" t="s">
+        <v>18</v>
+      </c>
+      <c r="I370" t="s">
+        <v>126</v>
+      </c>
+      <c r="J370" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="371" spans="1:10">
+      <c r="A371" t="s">
+        <v>451</v>
+      </c>
+      <c r="C371" t="s">
+        <v>2</v>
+      </c>
+      <c r="F371" t="s">
+        <v>450</v>
+      </c>
+      <c r="H371" t="s">
+        <v>452</v>
+      </c>
+      <c r="I371" t="s">
+        <v>126</v>
+      </c>
+      <c r="J371" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="372" spans="1:10">
+      <c r="A372" t="s">
+        <v>453</v>
+      </c>
+      <c r="E372" t="s">
+        <v>4</v>
+      </c>
+      <c r="H372" t="s">
+        <v>15</v>
+      </c>
+      <c r="I372" t="s">
+        <v>424</v>
+      </c>
+      <c r="J372" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="373" spans="1:10">
+      <c r="A373" t="s">
+        <v>454</v>
+      </c>
+      <c r="C373" t="s">
+        <v>2</v>
+      </c>
+      <c r="E373" t="s">
+        <v>4</v>
+      </c>
+      <c r="G373" t="s">
+        <v>6</v>
+      </c>
+      <c r="H373" t="s">
+        <v>15</v>
+      </c>
+      <c r="I373" t="s">
+        <v>28</v>
+      </c>
+      <c r="J373" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:XFD353">
     <sortState ref="A2:A353">
@@ -10770,7 +11003,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1785005472" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1791932052" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -10779,14 +11012,14 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1785005472" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1785005472" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:header xmlns:pm="smNativeData" id="1791932052" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1791932052" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1785005472" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1791932052" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/MovieCatalog.xlsx
+++ b/MovieCatalog.xlsx
@@ -16,17 +16,17 @@
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1791932052" val="1224" rev="124" rev64="64" revOS="1" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1791932052" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1791932052" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1791932052"/>
+      <pm:revision xmlns:pm="smNativeData" day="1792939907" val="1224" rev="124" rev64="64" revOS="1" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1792939907" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1792939907" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1792939907"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2258" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2260" uniqueCount="455">
   <si>
     <t>Movie Name</t>
   </si>
@@ -1516,7 +1516,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1791932052" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1792939907" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -1531,7 +1531,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1791932052" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1792939907" ulstyle="none" kern="1">
             <pm:latin face="Basic Sans" sz="200" lang="default"/>
             <pm:cs face="Basic Roman" sz="200" lang="default"/>
             <pm:ea face="Basic Roman" sz="200" lang="default"/>
@@ -1547,7 +1547,7 @@
       <vertAlign val="superscript"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1791932052" ulstyle="none" kern="1" ssSize="66" ssDistance="15">
+          <pm:charSpec xmlns:pm="smNativeData" id="1792939907" ulstyle="none" kern="1" ssSize="66" ssDistance="15">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -1563,7 +1563,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1791932052" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1792939907" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -1585,7 +1585,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1791932052" type="1" fgLvl="76" fgClr="00FFFF00" bgLvl="24" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1792939907" type="1" fgLvl="76" fgClr="00FFFF00" bgLvl="24" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1599,7 +1599,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1791932052" type="1" fgLvl="76" fgClr="00FFFF00" bgLvl="24" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1792939907" type="1" fgLvl="76" fgClr="00FFFF00" bgLvl="24" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1613,7 +1613,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1791932052" type="1" fgLvl="38" fgClr="00FFFF00" bgLvl="62" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1792939907" type="1" fgLvl="38" fgClr="00FFFF00" bgLvl="62" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1624,7 +1624,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1791932052" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1792939907" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1646,7 +1646,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1791932052"/>
+          <pm:border xmlns:pm="smNativeData" id="1792939907"/>
         </ext>
       </extLst>
     </border>
@@ -1665,7 +1665,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1791932052">
+          <pm:border xmlns:pm="smNativeData" id="1792939907">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1689,7 +1689,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1791932052">
+          <pm:border xmlns:pm="smNativeData" id="1792939907">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1713,7 +1713,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1791932052">
+          <pm:border xmlns:pm="smNativeData" id="1792939907">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1736,7 +1736,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1791932052">
+          <pm:border xmlns:pm="smNativeData" id="1792939907">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1759,7 +1759,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1791932052"/>
+          <pm:border xmlns:pm="smNativeData" id="1792939907"/>
         </ext>
       </extLst>
     </border>
@@ -1778,7 +1778,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1791932052"/>
+          <pm:border xmlns:pm="smNativeData" id="1792939907"/>
         </ext>
       </extLst>
     </border>
@@ -1801,10 +1801,10 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1791932052" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1792939907" count="1">
         <pm:charStyle name="Normal" fontId="0"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1791932052" count="2">
+      <pm:colors xmlns:pm="smNativeData" id="1792939907" count="2">
         <pm:color name="Color 24" rgb="FFFF3D"/>
         <pm:color name="Color 25" rgb="FFFF9E"/>
       </pm:colors>
@@ -4163,7 +4163,9 @@
       <c r="C87" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D87" s="2"/>
+      <c r="D87" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="E87" s="5"/>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
@@ -6525,7 +6527,9 @@
       </c>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
-      <c r="D185" s="2"/>
+      <c r="D185" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="E185" s="5" t="s">
         <v>4</v>
       </c>
@@ -11003,7 +11007,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1791932052" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1792939907" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -11012,14 +11016,14 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1791932052" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1791932052" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:header xmlns:pm="smNativeData" id="1792939907" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1792939907" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1791932052" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1792939907" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
